--- a/tools/importer/reports/import-member-healthcare.report.xlsx
+++ b/tools/importer/reports/import-member-healthcare.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>_reportFile</t>
   </si>
@@ -89,10 +89,31 @@
     <t>member-healthcare</t>
   </si>
   <si>
-    <t>2026-08-14T12:16:00.049Z</t>
+    <t>2026-08-14T14:38:06.046Z</t>
   </si>
   <si>
     <t>Financial Relief for Your Medical Costs</t>
+  </si>
+  <si>
+    <t>member/healthcare/i-lindung.report.json</t>
+  </si>
+  <si>
+    <t>["hero-product","cards-icon","cards-icon","cards-icon","cards-icon","accordion","accordion","accordion","accordion","cards-articles"]</t>
+  </si>
+  <si>
+    <t>member/healthcare/i-lindung</t>
+  </si>
+  <si>
+    <t>member-product</t>
+  </si>
+  <si>
+    <t>2026-08-14T13:45:03.962Z</t>
+  </si>
+  <si>
+    <t>i-Lindung: Purchase Insurance/Takaful</t>
+  </si>
+  <si>
+    <t>http://127.0.0.1:8788/member/healthcare/i-lindung.html</t>
   </si>
 </sst>
 </file>
@@ -481,17 +502,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="2" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="9" width="41" customWidth="1"/>
-    <col min="10" max="10" width="46" customWidth="1"/>
+    <col min="10" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -588,6 +608,38 @@
       </c>
       <c r="J3" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
